--- a/Result/profitability/1225.xlsx
+++ b/Result/profitability/1225.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>0.42625</v>
+        <v>0.2524999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>9.2475</v>
+        <v>8.72125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3925</v>
+        <v>0.21875</v>
       </c>
       <c r="N3" t="n">
-        <v>8.7075</v>
+        <v>8.02375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>-0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0.29125</v>
+        <v>0.1075</v>
       </c>
       <c r="N4" t="n">
-        <v>7.66</v>
+        <v>7.058750000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.10875</v>
+        <v>-0.08125000000000002</v>
       </c>
       <c r="N5" t="n">
-        <v>5.96625</v>
+        <v>5.3425</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07874999999999999</v>
+        <v>-0.1025</v>
       </c>
       <c r="N6" t="n">
-        <v>5.487500000000001</v>
+        <v>4.65375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08875</v>
+        <v>-0.11</v>
       </c>
       <c r="N7" t="n">
-        <v>5.17875</v>
+        <v>4.32375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>0.03249999999999999</v>
+        <v>-0.15875</v>
       </c>
       <c r="N8" t="n">
-        <v>4.41375</v>
+        <v>3.73875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.26</v>
       </c>
       <c r="M9" t="n">
-        <v>0.009999999999999988</v>
+        <v>0.01</v>
       </c>
       <c r="N9" t="n">
         <v>3.985</v>
@@ -1645,7 +1645,7 @@
         <v>0.24</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04750000000000001</v>
+        <v>-0.04749999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>3.6675</v>
@@ -1772,7 +1772,7 @@
         <v>0.11</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.03750000000000002</v>
+        <v>-0.03749999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>3.86875</v>
@@ -1899,7 +1899,7 @@
         <v>0.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06374999999999997</v>
+        <v>0.06375</v>
       </c>
       <c r="N12" t="n">
         <v>4.535</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2967</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2851</v>
+      </c>
+      <c r="E75" t="n">
+        <v>116</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-44</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.47%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-214</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-258</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-265</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.2025</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.69875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-3.477272727272728</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.5806451612903226</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.534883720930233</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5613048368953881</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
